--- a/script.xlsx
+++ b/script.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>The `add` function calculates the sum of two given arguments.</t>
+          <t>The `add` function computes the sum of two given numbers.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>This function provides a straightforward way to perform addition. It accepts two parameters, `a` and `b`. Internally, it uses the `+` operator to compute the sum of these two values. The resulting sum is then returned by the function.</t>
+          <t>This function takes two parameters, `a` and `b`, and returns their sum. It uses the standard addition operator (`+`) to perform the calculation. The core logic is contained in a single statement `return a + b;`, which evaluates the sum of the two inputs and immediately returns the result.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>- The `+` operator in JavaScript is used for both numeric addition and string concatenation. If either `a` or `b` is a string, the function will perform string concatenation instead of addition. For example, `add(5, "5")` would result in the string `"55"`. - To ensure correct mathematical addition, always provide numeric inputs for both parameters. **Output Example**: A numeric value representing the sum.</t>
+          <t>- For standard arithmetic addition, ensure both `a` and `b` are of the `Number` type. - If either `a` or `b` is a string, the `+` operator will perform string concatenation instead of numerical addition. For example, `add(5, "3")` would result in the string `"53"`. **Output Example**: A number representing the sum of the inputs.</t>
         </is>
       </c>
     </row>
@@ -548,19 +548,15 @@
           <t>The `factorial` function recursively calculates the factorial of a given non-negative integer.</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>* **`n`** (Number): The non-negative integer for which the factorial will be computed.</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="inlineStr"/>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>This function calculates the factorial of a number `n`, which is the product of all positive integers up to `n` (n!). It employs a recursive approach to achieve this. The function's logic is based on two main parts: 1. **Base Case**: The function first checks if the input `n` is less than or equal to 1. The factorial of 1 (1!) is 1, and the factorial of 0 (0!) is also defined as 1. This condition serves as the termination point for the recursion, preventing an infinite loop. When this conditi...</t>
+          <t>The `factorial` function is a recursive implementation designed to compute the factorial of a number `n`, which is the product of all positive integers up to `n`. The function operates based on two main cases: 1. **Base Case**: The recursion terminates when the input `n` is less than or equal to 1. In this scenario, the function returns `1`. This is because the factorial of 1 (`1!`) is 1, and the factorial of 0 (`0!`) is also defined as 1. 2. **Recursive Step**: If `n` is greater than 1, the ...</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>- The function is designed for non-negative integers. Providing a negative number will cause infinite recursion, leading to a "Maximum call stack size exceeded" error. - Due to the recursive implementation, very large values for `n` can also exhaust the call stack and cause a stack overflow error. - Factorial values grow very rapidly. For inputs larger than a certain threshold (e.g., `170`), the result may exceed JavaScript's standard number representation and return `Infinity`. **Output Exam...</t>
+          <t>- This function is recursive. Providing a very large number for `n` can lead to a "Maximum call stack size exceeded" error (stack overflow). - The function is intended for non-negative integers. Passing a negative number will result in infinite recursion and a stack overflow. - While it may accept floating-point numbers, the mathematical concept of a factorial is typically defined only for non-negative integers, and results for non-integers may not be meaningful. **Output Example**: The funct...</t>
         </is>
       </c>
     </row>
@@ -575,22 +571,22 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>The `greet` function logs a personalized greeting message to the console.</t>
+          <t>The `greet` function prints a personalized greeting message to the console.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>- `name` (string): The name to include in the greeting message.</t>
+          <t>- `name` (String): The name to be included in the greeting message.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>This function provides a simple mechanism for displaying a standardized greeting. It accepts a single argument, `name`. The core logic utilizes the `console.log` method to print a formatted string to the standard output, such as a web browser's developer console or a Node.js terminal. The output string is constructed using a template literal: `` `Hello, ${name}!` ``. The placeholder `${name}` within this string is dynamically substituted with the value passed to the `name` parameter upon func...</t>
+          <t>This function provides a simple way to display a standardized greeting. It accepts a single argument, `name`, which is expected to be a string. The core logic uses the `console.log` method to output a message to the standard output, such as a web browser's developer console or a Node.js terminal. The message is constructed using a template literal: `` `Hello, ${name}!` ``. The `${name}` placeholder is dynamically replaced with the value passed to the `name` parameter when the function is invo...</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>- This function does not return a value (`undefined`). Its primary purpose is to produce a side effect by logging output to the console. - While the `name` parameter is intended to be a string, JavaScript's type coercion will attempt to convert any passed argument into its string representation. For example, calling `greet(123)` will output "Hello, 123!".</t>
+          <t>- This function does not return a value (it implicitly returns `undefined`). Its sole purpose is to produce a side effect by logging output to the console. - While the `name` parameter is intended to be a string, JavaScript's type coercion will attempt to convert any passed value into its string representation for the output. For example, passing the number `123` will result in the output `"Hello, 123!"`.</t>
         </is>
       </c>
     </row>

--- a/script.xlsx
+++ b/script.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>The `add` function computes the sum of two given numbers.</t>
+          <t>The `add` function calculates the sum of two given arguments.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>This function takes two parameters, `a` and `b`, and returns their sum. It uses the standard addition operator (`+`) to perform the calculation. The core logic is contained in a single statement `return a + b;`, which evaluates the sum of the two inputs and immediately returns the result.</t>
+          <t>This function takes two parameters, `a` and `b`, and returns their sum. It uses the fundamental JavaScript addition operator (`+`) to perform the calculation. The expression `a + b` is evaluated, and the resulting value is returned by the function. It's important to understand the behavior of the `+` operator in JavaScript. While this function is intended for numeric addition, if one or both of the arguments are strings, the operator will perform string concatenation instead.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>- For standard arithmetic addition, ensure both `a` and `b` are of the `Number` type. - If either `a` or `b` is a string, the `+` operator will perform string concatenation instead of numerical addition. For example, `add(5, "3")` would result in the string `"53"`. **Output Example**: A number representing the sum of the inputs.</t>
+          <t>- This function is designed for adding two numbers. For predictable results, ensure both `a` and `b` are of the `Number` type. - The function does not include any type checking. If non-numeric arguments are provided, JavaScript's type coercion rules will apply, which may lead to unexpected results like string concatenation instead of arithmetic addition. **Output Example**: A numeric value representing the sum of the inputs, or a string if concatenation occurs.</t>
         </is>
       </c>
     </row>
@@ -548,15 +548,19 @@
           <t>The `factorial` function recursively calculates the factorial of a given non-negative integer.</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>- `n` (Number): The non-negative integer for which to calculate the factorial.</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>The `factorial` function is a recursive implementation designed to compute the factorial of a number `n`, which is the product of all positive integers up to `n`. The function operates based on two main cases: 1. **Base Case**: The recursion terminates when the input `n` is less than or equal to 1. In this scenario, the function returns `1`. This is because the factorial of 1 (`1!`) is 1, and the factorial of 0 (`0!`) is also defined as 1. 2. **Recursive Step**: If `n` is greater than 1, the ...</t>
+          <t>This function computes the factorial of a number `n` using a recursive approach. The factorial of a non-negative integer `n`, denoted by `n!`, is the product of all positive integers less than or equal to `n`. The function's logic is based on a ternary operator which serves as a compact `if-else` statement: 1. **Base Case:** The condition `n &lt;= 1` is checked first. If `n` is 0 or 1, the function returns `1`. This is the termination condition for the recursion, as the factorial of both 0 and 1...</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>- This function is recursive. Providing a very large number for `n` can lead to a "Maximum call stack size exceeded" error (stack overflow). - The function is intended for non-negative integers. Passing a negative number will result in infinite recursion and a stack overflow. - While it may accept floating-point numbers, the mathematical concept of a factorial is typically defined only for non-negative integers, and results for non-integers may not be meaningful. **Output Example**: The funct...</t>
+          <t>- This function is intended for non-negative integers. Providing a negative number will result in infinite recursion and cause a stack overflow error. - Due to the nature of recursion, calculating the factorial of very large numbers can lead to a "Maximum call stack size exceeded" error. For large-scale calculations, an iterative approach might be more memory-efficient. **Output Example**: The function returns a single number representing the calculated factorial.</t>
         </is>
       </c>
     </row>
@@ -576,17 +580,17 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>- `name` (String): The name to be included in the greeting message.</t>
+          <t>- `name` (`String`): The name to be included in the greeting message.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>This function provides a simple way to display a standardized greeting. It accepts a single argument, `name`, which is expected to be a string. The core logic uses the `console.log` method to output a message to the standard output, such as a web browser's developer console or a Node.js terminal. The message is constructed using a template literal: `` `Hello, ${name}!` ``. The `${name}` placeholder is dynamically replaced with the value passed to the `name` parameter when the function is invo...</t>
+          <t>This function provides a simple way to display a standard greeting. It accepts a single argument, `name`, which is expected to be a string. The core logic uses a template literal to construct the output string `Hello, ${name}!`. The `${name}` placeholder is dynamically replaced with the value of the `name` parameter provided during the function call. Finally, the fully constructed string is passed to the `console.log()` method, which outputs the message to the standard console. The function d...</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>- This function does not return a value (it implicitly returns `undefined`). Its sole purpose is to produce a side effect by logging output to the console. - While the `name` parameter is intended to be a string, JavaScript's type coercion will attempt to convert any passed value into its string representation for the output. For example, passing the number `123` will result in the output `"Hello, 123!"`.</t>
+          <t>- This function does not return a value (`undefined`); its sole purpose is to log a message to the console. - If a non-string value (e.g., a number or an object) is passed as the `name` parameter, JavaScript will attempt to convert it to its string representation for the output.</t>
         </is>
       </c>
     </row>

--- a/script.xlsx
+++ b/script.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code Documentation" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,44 +461,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Function No</t>
+          <t>Item No</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Function Name</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Parameters</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Usage Notes</t>
         </is>
@@ -510,27 +516,32 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
           <t>add(a, b)</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>The `add` function calculates the sum of two given arguments.</t>
-        </is>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Description | The first number to be added. | The second number to be added. |</t>
+          <t>The `add` function calculates the sum of two provided arguments.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>This function takes two parameters, `a` and `b`, and returns their sum. It uses the fundamental JavaScript addition operator (`+`) to perform the calculation. The expression `a + b` is evaluated, and the resulting value is returned by the function. It's important to understand the behavior of the `+` operator in JavaScript. While this function is intended for numeric addition, if one or both of the arguments are strings, the operator will perform string concatenation instead.</t>
+          <t>Description | The first number or addend. | The second number or addend. |</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>- This function is designed for adding two numbers. For predictable results, ensure both `a` and `b` are of the `Number` type. - The function does not include any type checking. If non-numeric arguments are provided, JavaScript's type coercion rules will apply, which may lead to unexpected results like string concatenation instead of arithmetic addition. **Output Example**: A numeric value representing the sum of the inputs, or a string if concatenation occurs.</t>
+          <t>This function takes two parameters, `a` and `b`, and returns their sum. It uses the standard addition operator (`+`) to perform the calculation. The function is straightforward and directly returns the result of `a + b`. For example, if `a` is `5` and `b` is `10`, the function will compute `5 + 10` and return the value `15`.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>- This function is designed for numeric inputs (integers or floating-point numbers). - If string values are provided, the `+` operator in JavaScript will perform string concatenation instead of arithmetic addition. For example, `add("5", "10")` would result in the string `"510"`. - The function handles both positive and negative numbers. **Output Example**: A numeric value representing the sum.</t>
         </is>
       </c>
     </row>
@@ -540,27 +551,32 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>factorial(n)</t>
+          <t>FunctionDef</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>The `factorial` function recursively calculates the factorial of a given non-negative integer.</t>
+          <t>add</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>- `n` (Number): The non-negative integer for which to calculate the factorial.</t>
+          <t>The `add` function is intended to calculate the sum of two numbers.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>This function computes the factorial of a number `n` using a recursive approach. The factorial of a non-negative integer `n`, denoted by `n!`, is the product of all positive integers less than or equal to `n`. The function's logic is based on a ternary operator which serves as a compact `if-else` statement: 1. **Base Case:** The condition `n &lt;= 1` is checked first. If `n` is 0 or 1, the function returns `1`. This is the termination condition for the recursion, as the factorial of both 0 and 1...</t>
+          <t>Description | The first number to be added. | The second number to be added. |</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>- This function is intended for non-negative integers. Providing a negative number will result in infinite recursion and cause a stack overflow error. - Due to the nature of recursion, calculating the factorial of very large numbers can lead to a "Maximum call stack size exceeded" error. For large-scale calculations, an iterative approach might be more memory-efficient. **Output Example**: The function returns a single number representing the calculated factorial.</t>
+          <t>This function is designed to accept two arguments, `a` and `b`, and return their sum. As currently written, the function is a stub with an empty body. It does not contain any logic to perform the addition. Therefore, when called, it will execute without performing any operations and will implicitly return `undefined`. To make the function operational, it must be implemented to return the sum of its parameters. A correct implementation would be:</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>- This function is currently a placeholder and does not perform any calculation in its present state. - Calling the function as is will always result in a return value of `undefined`. - The function must be completed by adding the return statement `return a + b;` to fulfill its intended purpose.</t>
         </is>
       </c>
     </row>
@@ -570,27 +586,133 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>factorial(n)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>The `factorial` function recursively calculates the factorial of a given non-negative integer.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>This function computes the factorial of a number `n` using a recursive approach. The factorial of a non-negative integer `n`, denoted by `n!`, is the product of all positive integers less than or equal to `n`. The function's logic is based on two main cases: 1. **Base Case**: The recursion terminates when `n` is less than or equal to 1. By definition, the factorial of 0 (`0!`) and 1 (`1!`) is 1. In this case, the function returns `1`. 2. **Recursive Step**: If `n` is greater than 1, the funct...</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>- This function is designed for non-negative integers. Providing a negative number will cause infinite recursion, leading to a "Maximum call stack size exceeded" error. - Due to its recursive nature, calculating the factorial of very large numbers can also lead to a stack overflow error. For such cases, an iterative approach might be more suitable. - The input `n` is expected to be an integer. While it may work for floating-point numbers until the base case, the mathematical concept of a fact...</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>factorial</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>The `factorial` function calculates and returns the factorial of a non-negative integer.</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>- `n`: `Number` - The non-negative integer for which to calculate the factorial.</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>This function computes the factorial of a given number `n`. The factorial of a non-negative integer `n`, denoted as `n!`, is the product of all positive integers less than or equal to `n`. For example, `5!` is `5 * 4 * 3 * 2 * 1`, which equals `120`. The function is typically implemented using recursion. It operates based on two primary cases: 1. **Base Case:** If `n` is `0` or `1`, the function returns `1`. By mathematical definition, the factorial of 0 (`0!`) is 1, and the factorial of 1 (`...</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>- This function is designed for non-negative integers. Passing a negative number as an argument will not yield a valid factorial. - Factorial values increase very quickly. For inputs larger than `170`, the result may exceed JavaScript's maximum representable number (`Number.MAX_VALUE`) and return `Infinity`. - When using a recursive implementation for this function, very large numbers for `n` can potentially cause a "Maximum call stack size exceeded" error. For such scenarios, an iterative ap...</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
           <t>greet(name)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>The `greet` function prints a personalized greeting message to the console.</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>- `name` (`String`): The name to be included in the greeting message.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>This function provides a simple way to display a standard greeting. It accepts a single argument, `name`, which is expected to be a string. The core logic uses a template literal to construct the output string `Hello, ${name}!`. The `${name}` placeholder is dynamically replaced with the value of the `name` parameter provided during the function call. Finally, the fully constructed string is passed to the `console.log()` method, which outputs the message to the standard console. The function d...</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>- This function does not return a value (`undefined`); its sole purpose is to log a message to the console. - If a non-string value (e.g., a number or an object) is passed as the `name` parameter, JavaScript will attempt to convert it to its string representation for the output.</t>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>The `greet` function logs a personalized greeting message to the console.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>- `name` (String): The name to be included in the greeting message.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>This function provides a simple way to display a standardized greeting. It takes a single parameter, `name`, which is intended to be a string. The core logic resides within a `console.log()` statement. It utilizes a template literal (`` ` ``) to construct the output string. The string `Hello, ` is combined with the value of the `name` parameter, followed by an exclamation mark `!`. The resulting string is then printed directly to the console. For example, if the string `"World"` is passed as ...</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>- This function does not return a value; its primary effect is the side effect of printing to the console. - If a non-string value (e.g., a number or an object) is passed as the `name` parameter, JavaScript will attempt to convert it to its string representation before printing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>FunctionDef</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>greet</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>The `greet` function is a placeholder intended to perform a greeting action using the provided name.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>- `name`: **any** - The name to be used in the greeting. The intended type is likely a string.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>The `greet` function is defined to accept a single argument, `name`. The function body is currently empty, meaning it contains no executable code. As a result, when this function is called, it performs no actions and does not produce any output. In JavaScript, a function that does not have an explicit `return` statement will implicitly return `undefined`. This function serves as a stub or placeholder for future implementation.</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>- As the function body is empty, calling `greet` will have no side effects (e.g., no console output). - The function will always return `undefined` in its current state. - This function must be implemented with logic to be useful for its intended purpose of greeting.</t>
         </is>
       </c>
     </row>

--- a/script.xlsx
+++ b/script.xlsx
@@ -526,22 +526,22 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `add` function calculates the sum of two provided arguments.</t>
+          <t>The `add` function computes the sum of two numbers and returns the result.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Description | The first number or addend. | The second number or addend. |</t>
+          <t>Description | The first number to be added. | The second number to be added. |</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>This function takes two parameters, `a` and `b`, and returns their sum. It uses the standard addition operator (`+`) to perform the calculation. The function is straightforward and directly returns the result of `a + b`. For example, if `a` is `5` and `b` is `10`, the function will compute `5 + 10` and return the value `15`.</t>
+          <t>This function provides a basic arithmetic operation. It takes two parameters, `a` and `b`, which are intended to be numeric values. The core logic of the function uses the standard JavaScript addition operator (`+`) to sum the two input values. The result of this calculation is then returned by the function.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- This function is designed for numeric inputs (integers or floating-point numbers). - If string values are provided, the `+` operator in JavaScript will perform string concatenation instead of arithmetic addition. For example, `add("5", "10")` would result in the string `"510"`. - The function handles both positive and negative numbers. **Output Example**: A numeric value representing the sum.</t>
+          <t>- This function is designed for numeric addition. While the JavaScript `+` operator can also perform string concatenation, passing string arguments to this function will result in concatenation rather than mathematical addition (e.g., `add("2", "3")` will return `"23"`). - The function works correctly with both integer and floating-point numbers. **Output Example**: A single numeric value representing the sum.</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `add` function is intended to calculate the sum of two numbers.</t>
+          <t>The `add` function is a placeholder intended to calculate the sum of two numbers.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>This function is designed to accept two arguments, `a` and `b`, and return their sum. As currently written, the function is a stub with an empty body. It does not contain any logic to perform the addition. Therefore, when called, it will execute without performing any operations and will implicitly return `undefined`. To make the function operational, it must be implemented to return the sum of its parameters. A correct implementation would be:</t>
+          <t>This function is designed to accept two numerical arguments, `a` and `b`. The intended purpose is to compute their sum and return the result. However, the current implementation is an empty stub. It does not contain any operational logic to perform the addition. Consequently, when called, it does not perform any calculation and implicitly returns `undefined`.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- This function is currently a placeholder and does not perform any calculation in its present state. - Calling the function as is will always result in a return value of `undefined`. - The function must be completed by adding the return statement `return a + b;` to fulfill its intended purpose.</t>
+          <t>- This function is a placeholder and is not yet implemented. - To use this function as intended, you must add the addition logic (e.g., `return a + b;`) to the function body. - Calling the function in its current state will always result in `undefined`.</t>
         </is>
       </c>
     </row>
@@ -599,15 +599,19 @@
           <t>The `factorial` function recursively calculates the factorial of a given non-negative integer.</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>- `n` (Number): The non-negative integer for which the factorial will be calculated.</t>
+        </is>
+      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function computes the factorial of a number `n` using a recursive approach. The factorial of a non-negative integer `n`, denoted by `n!`, is the product of all positive integers less than or equal to `n`. The function's logic is based on two main cases: 1. **Base Case**: The recursion terminates when `n` is less than or equal to 1. By definition, the factorial of 0 (`0!`) and 1 (`1!`) is 1. In this case, the function returns `1`. 2. **Recursive Step**: If `n` is greater than 1, the funct...</t>
+          <t>This function computes the factorial of a number `n` using a recursive approach. The factorial of a non-negative integer `n`, denoted by `n!`, is the product of all positive integers less than or equal to `n`. The function's logic is based on a ternary operator which serves as a compact conditional statement: 1. **Base Case**: The recursion terminates when the input `n` is less than or equal to 1. In this scenario, the function returns `1`. This handles two fundamental cases: the factorial of...</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- This function is designed for non-negative integers. Providing a negative number will cause infinite recursion, leading to a "Maximum call stack size exceeded" error. - Due to its recursive nature, calculating the factorial of very large numbers can also lead to a stack overflow error. For such cases, an iterative approach might be more suitable. - The input `n` is expected to be an integer. While it may work for floating-point numbers until the base case, the mathematical concept of a fact...</t>
+          <t>- This function is intended for non-negative integers. Passing a negative number as an argument will lead to infinite recursion, ultimately causing a "Maximum call stack size exceeded" error. - Be mindful of JavaScript's limitations with deep recursion. Calculating the factorial of very large numbers can exhaust the call stack. For such cases, an iterative approach is generally safer and more memory-efficient. - The function correctly handles `factorial(0)` and `factorial(1)`, both of which r...</t>
         </is>
       </c>
     </row>
@@ -627,22 +631,22 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>The `factorial` function calculates and returns the factorial of a non-negative integer.</t>
+          <t>The `factorial` function calculates the factorial of a given non-negative integer.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>- `n`: `Number` - The non-negative integer for which to calculate the factorial.</t>
+          <t>- `n`: The non-negative integer for which to calculate the factorial.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>This function computes the factorial of a given number `n`. The factorial of a non-negative integer `n`, denoted as `n!`, is the product of all positive integers less than or equal to `n`. For example, `5!` is `5 * 4 * 3 * 2 * 1`, which equals `120`. The function is typically implemented using recursion. It operates based on two primary cases: 1. **Base Case:** If `n` is `0` or `1`, the function returns `1`. By mathematical definition, the factorial of 0 (`0!`) is 1, and the factorial of 1 (`...</t>
+          <t>This function computes the factorial of a number `n`, which is the product of all positive integers up to `n`. The factorial of `n` is denoted as `n!`. By mathematical convention, the factorial of 0 is 1. The function is implemented using recursion. It has two main parts: 1. **Base Case**: The recursion terminates when the input `n` is `0` or `1`. In this case, the function returns `1`, as `0! = 1` and `1! = 1`. This prevents an infinite loop of recursive calls. 2. **Recursive Step**: If `n` ...</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>- This function is designed for non-negative integers. Passing a negative number as an argument will not yield a valid factorial. - Factorial values increase very quickly. For inputs larger than `170`, the result may exceed JavaScript's maximum representable number (`Number.MAX_VALUE`) and return `Infinity`. - When using a recursive implementation for this function, very large numbers for `n` can potentially cause a "Maximum call stack size exceeded" error. For such scenarios, an iterative ap...</t>
+          <t>- This function is intended for non-negative integers. Providing a negative number will cause infinite recursion, leading to a "Maximum call stack size exceeded" error. - Factorial values grow very rapidly. Using large numbers for `n` can result in values that exceed JavaScript's `Number.MAX_SAFE_INTEGER`, which may lead to a loss of precision or return `Infinity`. - The input `n` should be an integer. Passing a non-integer value may produce unexpected results.</t>
         </is>
       </c>
     </row>
@@ -667,17 +671,17 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>- `name` (String): The name to be included in the greeting message.</t>
+          <t>- `name` (string): The name of the person or entity to be greeted. This value will be embedded in the output message.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>This function provides a simple way to display a standardized greeting. It takes a single parameter, `name`, which is intended to be a string. The core logic resides within a `console.log()` statement. It utilizes a template literal (`` ` ``) to construct the output string. The string `Hello, ` is combined with the value of the `name` parameter, followed by an exclamation mark `!`. The resulting string is then printed directly to the console. For example, if the string `"World"` is passed as ...</t>
+          <t>This function provides a simple way to display a standard greeting. It accepts a single argument, `name`. The core logic uses the `console.log()` method to print a message to the standard output, which is typically the web browser's developer console or the terminal in a Node.js environment. The message is constructed using a JavaScript template literal: `` `Hello, ${name}!` ``. This allows the value of the `name` parameter to be directly interpolated into the string, creating a personalized ...</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>- This function does not return a value; its primary effect is the side effect of printing to the console. - If a non-string value (e.g., a number or an object) is passed as the `name` parameter, JavaScript will attempt to convert it to its string representation before printing.</t>
+          <t>- This function does not return a value (it implicitly returns `undefined`). Its primary effect is logging output to the console. - While the `name` parameter is intended to be a string, JavaScript's type coercion will attempt to convert any passed-in value to its string representation. For example, passing the number `123` will result in the output "Hello, 123!".</t>
         </is>
       </c>
     </row>
@@ -702,17 +706,17 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>- `name`: **any** - The name to be used in the greeting. The intended type is likely a string.</t>
+          <t>- `name` (any): The name of the person or entity to be greeted.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>The `greet` function is defined to accept a single argument, `name`. The function body is currently empty, meaning it contains no executable code. As a result, when this function is called, it performs no actions and does not produce any output. In JavaScript, a function that does not have an explicit `return` statement will implicitly return `undefined`. This function serves as a stub or placeholder for future implementation.</t>
+          <t>The `greet` function is defined to accept a single parameter, `name`. The intended purpose is to use this `name` to construct and display or return a greeting message. However, in its current state, the function body is empty. Consequently, when `greet` is called, it executes no operations and does not explicitly return a value. In JavaScript, a function that does not have a `return` statement implicitly returns `undefined`.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>- As the function body is empty, calling `greet` will have no side effects (e.g., no console output). - The function will always return `undefined` in its current state. - This function must be implemented with logic to be useful for its intended purpose of greeting.</t>
+          <t>- This function currently serves as a stub or placeholder and lacks any implementation. - To make this function useful, you must add logic to its body. For example, you could use `console.log` to print a greeting to the console or use a `return` statement to send back a greeting string.</t>
         </is>
       </c>
     </row>

--- a/script.xlsx
+++ b/script.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -526,7 +526,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `add` function computes the sum of two numbers and returns the result.</t>
+          <t>The `add` function computes the sum of two given numbers.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>This function provides a basic arithmetic operation. It takes two parameters, `a` and `b`, which are intended to be numeric values. The core logic of the function uses the standard JavaScript addition operator (`+`) to sum the two input values. The result of this calculation is then returned by the function.</t>
+          <t>The `add` function provides a basic arithmetic operation. It takes two parameters, `a` and `b`, which are expected to be numbers. The function uses the standard addition operator (`+`) to calculate the sum of these two values. The result of this operation is then returned by the function. For example, if `a` is `10` and `b` is `5`, the function will compute `10 + 5` and return the value `15`.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- This function is designed for numeric addition. While the JavaScript `+` operator can also perform string concatenation, passing string arguments to this function will result in concatenation rather than mathematical addition (e.g., `add("2", "3")` will return `"23"`). - The function works correctly with both integer and floating-point numbers. **Output Example**: A single numeric value representing the sum.</t>
+          <t>- This function is designed for numerical addition. If string values are passed as arguments, the `+` operator will perform string concatenation instead of addition. For example, `add("Hello, ", "World!")` would return `"Hello, World!"`. - To ensure correct arithmetic, always pass arguments of the `Number` type. Passing mixed types (e.g., a number and a string) will result in type coercion and string concatenation. **Output Example**: A typical return value for numerical inputs.</t>
         </is>
       </c>
     </row>
@@ -556,27 +556,27 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>add</t>
+          <t>factorial(n)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `add` function is a placeholder intended to calculate the sum of two numbers.</t>
+          <t>The `factorial` function recursively calculates the factorial of a given non-negative integer.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Description | The first number to be added. | The second number to be added. |</t>
+          <t>- `n` (Number): The non-negative integer for which the factorial will be calculated.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>This function is designed to accept two numerical arguments, `a` and `b`. The intended purpose is to compute their sum and return the result. However, the current implementation is an empty stub. It does not contain any operational logic to perform the addition. Consequently, when called, it does not perform any calculation and implicitly returns `undefined`.</t>
+          <t>This function computes the factorial of a number `n` using a recursive approach. The factorial of a non-negative integer `n`, denoted by `n!`, is the product of all positive integers less than or equal to `n`. The function's logic is based on a ternary operator which serves as a compact `if-else` statement: 1. **Base Case**: It first checks if the input `n` is less than or equal to 1. If it is, the function returns `1`. This is the termination condition for the recursion, as the factorial of ...</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- This function is a placeholder and is not yet implemented. - To use this function as intended, you must add the addition logic (e.g., `return a + b;`) to the function body. - Calling the function in its current state will always result in `undefined`.</t>
+          <t>- The function is designed for non-negative integers. Providing a negative number will cause infinite recursion, leading to a "Maximum call stack size exceeded" error. - Be aware of JavaScript's number limitations. Calculating the factorial of very large numbers can result in a stack overflow due to deep recursion or return `Infinity` if the result exceeds the maximum value for a standard number. - The base cases `factorial(0)` and `factorial(1)` will both correctly return `1`. **Output Examp...</t>
         </is>
       </c>
     </row>
@@ -591,132 +591,27 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>factorial(n)</t>
+          <t>greet(name)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>The `factorial` function recursively calculates the factorial of a given non-negative integer.</t>
+          <t>The `greet` function logs a personalized greeting message to the console.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>- `n` (Number): The non-negative integer for which the factorial will be calculated.</t>
+          <t>- `name` (`string`): The name to be included in the greeting message.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function computes the factorial of a number `n` using a recursive approach. The factorial of a non-negative integer `n`, denoted by `n!`, is the product of all positive integers less than or equal to `n`. The function's logic is based on a ternary operator which serves as a compact conditional statement: 1. **Base Case**: The recursion terminates when the input `n` is less than or equal to 1. In this scenario, the function returns `1`. This handles two fundamental cases: the factorial of...</t>
+          <t>This function provides a simple way to display a standardized greeting. It accepts a single argument, `name`. The core logic uses the `console.log()` method to print a formatted string to the web console. The message is constructed using a template literal: `` `Hello, ${name}!` ``. The `${name}` expression within the string is a placeholder that is dynamically replaced by the value passed into the `name` parameter, creating a personalized output.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- This function is intended for non-negative integers. Passing a negative number as an argument will lead to infinite recursion, ultimately causing a "Maximum call stack size exceeded" error. - Be mindful of JavaScript's limitations with deep recursion. Calculating the factorial of very large numbers can exhaust the call stack. For such cases, an iterative approach is generally safer and more memory-efficient. - The function correctly handles `factorial(0)` and `factorial(1)`, both of which r...</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>FunctionDef</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>factorial</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>The `factorial` function calculates the factorial of a given non-negative integer.</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>- `n`: The non-negative integer for which to calculate the factorial.</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>This function computes the factorial of a number `n`, which is the product of all positive integers up to `n`. The factorial of `n` is denoted as `n!`. By mathematical convention, the factorial of 0 is 1. The function is implemented using recursion. It has two main parts: 1. **Base Case**: The recursion terminates when the input `n` is `0` or `1`. In this case, the function returns `1`, as `0! = 1` and `1! = 1`. This prevents an infinite loop of recursive calls. 2. **Recursive Step**: If `n` ...</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>- This function is intended for non-negative integers. Providing a negative number will cause infinite recursion, leading to a "Maximum call stack size exceeded" error. - Factorial values grow very rapidly. Using large numbers for `n` can result in values that exceed JavaScript's `Number.MAX_SAFE_INTEGER`, which may lead to a loss of precision or return `Infinity`. - The input `n` should be an integer. Passing a non-integer value may produce unexpected results.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>FunctionDef</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>greet(name)</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>The `greet` function logs a personalized greeting message to the console.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>- `name` (string): The name of the person or entity to be greeted. This value will be embedded in the output message.</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>This function provides a simple way to display a standard greeting. It accepts a single argument, `name`. The core logic uses the `console.log()` method to print a message to the standard output, which is typically the web browser's developer console or the terminal in a Node.js environment. The message is constructed using a JavaScript template literal: `` `Hello, ${name}!` ``. This allows the value of the `name` parameter to be directly interpolated into the string, creating a personalized ...</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>- This function does not return a value (it implicitly returns `undefined`). Its primary effect is logging output to the console. - While the `name` parameter is intended to be a string, JavaScript's type coercion will attempt to convert any passed-in value to its string representation. For example, passing the number `123` will result in the output "Hello, 123!".</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>FunctionDef</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>greet</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>The `greet` function is a placeholder intended to perform a greeting action using the provided name.</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>- `name` (any): The name of the person or entity to be greeted.</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>The `greet` function is defined to accept a single parameter, `name`. The intended purpose is to use this `name` to construct and display or return a greeting message. However, in its current state, the function body is empty. Consequently, when `greet` is called, it executes no operations and does not explicitly return a value. In JavaScript, a function that does not have a `return` statement implicitly returns `undefined`.</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>- This function currently serves as a stub or placeholder and lacks any implementation. - To make this function useful, you must add logic to its body. For example, you could use `console.log` to print a greeting to the console or use a `return` statement to send back a greeting string.</t>
+          <t>- This function does not return a value; its primary effect is the side effect of printing output to the console. - While the `name` parameter is expected to be a string for the intended output, JavaScript's type coercion will convert non-string arguments into their string representation when embedded in the template literal.</t>
         </is>
       </c>
     </row>

--- a/script.xlsx
+++ b/script.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `add` function computes the sum of two given numbers.</t>
+          <t>The `add` function computes the sum of two numbers.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>The `add` function provides a basic arithmetic operation. It takes two parameters, `a` and `b`, which are expected to be numbers. The function uses the standard addition operator (`+`) to calculate the sum of these two values. The result of this operation is then returned by the function. For example, if `a` is `10` and `b` is `5`, the function will compute `10 + 5` and return the value `15`.</t>
+          <t>The `add` function provides a simple mechanism for performing addition. It takes two parameters, `a` and `b`, which are expected to be numbers. The core logic of the function uses the standard addition operator (`+`) to calculate the sum of these two parameters. The result of this operation is then returned as the function's output.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- This function is designed for numerical addition. If string values are passed as arguments, the `+` operator will perform string concatenation instead of addition. For example, `add("Hello, ", "World!")` would return `"Hello, World!"`. - To ensure correct arithmetic, always pass arguments of the `Number` type. Passing mixed types (e.g., a number and a string) will result in type coercion and string concatenation. **Output Example**: A typical return value for numerical inputs.</t>
+          <t>- This function is intended for numeric addition. If non-numeric types (like strings) are passed, JavaScript's `+` operator will perform concatenation instead of mathematical addition, which may lead to unexpected behavior. - The function correctly handles both integer and floating-point numbers. **Output Example**: A successful call to `add(10, 5)` will return the number `15`.</t>
         </is>
       </c>
     </row>
@@ -571,12 +571,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>This function computes the factorial of a number `n` using a recursive approach. The factorial of a non-negative integer `n`, denoted by `n!`, is the product of all positive integers less than or equal to `n`. The function's logic is based on a ternary operator which serves as a compact `if-else` statement: 1. **Base Case**: It first checks if the input `n` is less than or equal to 1. If it is, the function returns `1`. This is the termination condition for the recursion, as the factorial of ...</t>
+          <t>This function implements the mathematical concept of a factorial, denoted as `n!`, which is the product of all positive integers up to `n`. The implementation uses recursion to achieve this. The core logic is contained within a single conditional (ternary) expression: `n &lt;= 1 ? 1 : n * factorial(n - 1)`. 1. **Base Case**: The recursion terminates when the input `n` is less than or equal to 1. By definition, the factorial of 1 (`1!`) is 1, and the factorial of 0 (`0!`) is also 1. The function ...</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- The function is designed for non-negative integers. Providing a negative number will cause infinite recursion, leading to a "Maximum call stack size exceeded" error. - Be aware of JavaScript's number limitations. Calculating the factorial of very large numbers can result in a stack overflow due to deep recursion or return `Infinity` if the result exceeds the maximum value for a standard number. - The base cases `factorial(0)` and `factorial(1)` will both correctly return `1`. **Output Examp...</t>
+          <t>- This function is recursive. Providing a very large number as input can lead to a "Maximum call stack size exceeded" error, as each recursive call consumes memory on the call stack. - The function is intended for non-negative integers. Passing a negative number will cause an infinite recursion, ultimately resulting in a stack overflow. - While the function will execute with floating-point numbers, the factorial concept is traditionally defined only for non-negative integers. **Output Example...</t>
         </is>
       </c>
     </row>
@@ -601,17 +601,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>- `name` (`string`): The name to be included in the greeting message.</t>
+          <t>- `name` (string): The name to be included in the greeting message.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function provides a simple way to display a standardized greeting. It accepts a single argument, `name`. The core logic uses the `console.log()` method to print a formatted string to the web console. The message is constructed using a template literal: `` `Hello, ${name}!` ``. The `${name}` expression within the string is a placeholder that is dynamically replaced by the value passed into the `name` parameter, creating a personalized output.</t>
+          <t>The `greet` function provides a simple way to display a formatted greeting. It accepts a single string argument, `name`. The function's core logic uses `console.log()` to print a message to the standard output, typically the browser's developer console or a terminal environment. The message itself is constructed using a JavaScript template literal: `` `Hello, ${name}!` ``. This syntax allows the value of the `name` parameter to be directly embedded within the string, creating a personalized g...</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- This function does not return a value; its primary effect is the side effect of printing output to the console. - While the `name` parameter is expected to be a string for the intended output, JavaScript's type coercion will convert non-string arguments into their string representation when embedded in the template literal.</t>
+          <t>- This function does not return any value; its sole purpose is to produce a side effect by logging output to the console. - While the `name` parameter is expected to be a string, JavaScript's type coercion will attempt to convert any non-string value passed to it into a string for the output. For instance, `greet(123)` will log "Hello, 123!".</t>
         </is>
       </c>
     </row>

--- a/script.xlsx
+++ b/script.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `add` function computes the sum of two numbers.</t>
+          <t>The `add` function calculates the sum of two numbers.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>The `add` function provides a simple mechanism for performing addition. It takes two parameters, `a` and `b`, which are expected to be numbers. The core logic of the function uses the standard addition operator (`+`) to calculate the sum of these two parameters. The result of this operation is then returned as the function's output.</t>
+          <t>The `add` function takes two parameters, `a` and `b`. It uses the standard addition operator (`+`) to compute the sum of these two values. The result of this operation is then returned by the function.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- This function is intended for numeric addition. If non-numeric types (like strings) are passed, JavaScript's `+` operator will perform concatenation instead of mathematical addition, which may lead to unexpected behavior. - The function correctly handles both integer and floating-point numbers. **Output Example**: A successful call to `add(10, 5)` will return the number `15`.</t>
+          <t>- This function is designed for numeric inputs. If strings are provided, JavaScript's `+` operator will perform string concatenation instead of addition (e.g., `add(5, "10")` will return `"510"`). - The function works correctly with both integer and floating-point numbers. **Output Example**: A numeric value representing the sum of the inputs. For example, if `a` is `5` and `b` is `10`, the output will be `15`.</t>
         </is>
       </c>
     </row>
@@ -566,17 +566,17 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>- `n` (Number): The non-negative integer for which the factorial will be calculated.</t>
+          <t>- `n`: `Number` - The non-negative integer for which to calculate the factorial.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>This function implements the mathematical concept of a factorial, denoted as `n!`, which is the product of all positive integers up to `n`. The implementation uses recursion to achieve this. The core logic is contained within a single conditional (ternary) expression: `n &lt;= 1 ? 1 : n * factorial(n - 1)`. 1. **Base Case**: The recursion terminates when the input `n` is less than or equal to 1. By definition, the factorial of 1 (`1!`) is 1, and the factorial of 0 (`0!`) is also 1. The function ...</t>
+          <t>This function implements the factorial operation, which is the product of all positive integers up to a given number `n` (denoted as `n!`). It uses a recursive approach to achieve this. The core logic is based on a conditional (ternary) operator: `n &lt;= 1 ? 1 : n * factorial(n - 1)`. 1. **Base Case**: The recursion terminates when the input `n` is less than or equal to 1. According to the definition of factorials, the factorial of 1 (`1!`) is 1, and the factorial of 0 (`0!`) is also 1. The con...</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- This function is recursive. Providing a very large number as input can lead to a "Maximum call stack size exceeded" error, as each recursive call consumes memory on the call stack. - The function is intended for non-negative integers. Passing a negative number will cause an infinite recursion, ultimately resulting in a stack overflow. - While the function will execute with floating-point numbers, the factorial concept is traditionally defined only for non-negative integers. **Output Example...</t>
+          <t>- This function is intended for non-negative integers. Providing a negative number will cause infinite recursion, leading to a "Maximum call stack size exceeded" error. - For very large values of `n`, this recursive implementation may exceed the JavaScript engine's call stack limit. An iterative approach is recommended for calculating factorials of very large numbers to avoid stack overflow errors. - The function does not perform type or value checking on the input `n`. Passing non-integer va...</t>
         </is>
       </c>
     </row>
@@ -601,17 +601,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>- `name` (string): The name to be included in the greeting message.</t>
+          <t>- `name` (String): The name to include in the greeting message.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>The `greet` function provides a simple way to display a formatted greeting. It accepts a single string argument, `name`. The function's core logic uses `console.log()` to print a message to the standard output, typically the browser's developer console or a terminal environment. The message itself is constructed using a JavaScript template literal: `` `Hello, ${name}!` ``. This syntax allows the value of the `name` parameter to be directly embedded within the string, creating a personalized g...</t>
+          <t>This function provides a simple way to display a standardized greeting to the console. It takes a single parameter, `name`, which is expected to be a string. The core logic uses the `console.log` method to print a formatted string. The string is created using a template literal (enclosed in backticks `` ` ``), which allows for the direct embedding of variables. The value of the `name` parameter is interpolated into the string `Hello, ${name}!` to generate the final output message.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- This function does not return any value; its sole purpose is to produce a side effect by logging output to the console. - While the `name` parameter is expected to be a string, JavaScript's type coercion will attempt to convert any non-string value passed to it into a string for the output. For instance, `greet(123)` will log "Hello, 123!".</t>
+          <t>- This function does not return a value (`undefined`). Its primary purpose is to produce a side effect by printing output to the console. - While the function is designed to work with a string `name`, JavaScript's type coercion will convert non-string arguments into their string representation. For example, calling `greet(123)` will output "Hello, 123!".</t>
         </is>
       </c>
     </row>

--- a/script.xlsx
+++ b/script.xlsx
@@ -466,7 +466,7 @@
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
@@ -521,12 +521,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>add(a, b)</t>
+          <t>add</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>The `add` function calculates the sum of two numbers.</t>
+          <t>The `add` function computes the sum of two numbers.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>The `add` function takes two parameters, `a` and `b`. It uses the standard addition operator (`+`) to compute the sum of these two values. The result of this operation is then returned by the function.</t>
+          <t>This function takes two arguments, `a` and `b`, and returns their sum. It uses the standard addition operator (`+`) to perform the calculation. The function is a straightforward implementation of arithmetic addition for numeric inputs.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- This function is designed for numeric inputs. If strings are provided, JavaScript's `+` operator will perform string concatenation instead of addition (e.g., `add(5, "10")` will return `"510"`). - The function works correctly with both integer and floating-point numbers. **Output Example**: A numeric value representing the sum of the inputs. For example, if `a` is `5` and `b` is `10`, the output will be `15`.</t>
+          <t>- This function is designed to work with numeric types (integers or floating-point numbers). - If strings are passed as arguments, the `+` operator will perform string concatenation instead of numeric addition due to JavaScript's type coercion. For example, `add("2", "3")` would result in `"23"`. - To ensure proper addition, make sure both inputs are numbers before calling the function. **Output Example**: The function returns a single `number` which is the sum of the two input parameters.</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>factorial(n)</t>
+          <t>factorial</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -566,17 +566,17 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>- `n`: `Number` - The non-negative integer for which to calculate the factorial.</t>
+          <t>- `n` (Number): The non-negative integer whose factorial is to be calculated.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>This function implements the factorial operation, which is the product of all positive integers up to a given number `n` (denoted as `n!`). It uses a recursive approach to achieve this. The core logic is based on a conditional (ternary) operator: `n &lt;= 1 ? 1 : n * factorial(n - 1)`. 1. **Base Case**: The recursion terminates when the input `n` is less than or equal to 1. According to the definition of factorials, the factorial of 1 (`1!`) is 1, and the factorial of 0 (`0!`) is also 1. The con...</t>
+          <t>This function implements the factorial operation using recursion. The logic is divided into two main parts: a base case and a recursive step. The function first evaluates the base case using a ternary operator: `n &lt;= 1 ? 1 : ...`. If the input number `n` is less than or equal to 1, the function immediately returns `1`. This is the termination condition for the recursion, as the factorial of 1 (1!) and 0 (0!) are both defined as 1. If `n` is greater than 1, the function executes the recursive ...</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- This function is intended for non-negative integers. Providing a negative number will cause infinite recursion, leading to a "Maximum call stack size exceeded" error. - For very large values of `n`, this recursive implementation may exceed the JavaScript engine's call stack limit. An iterative approach is recommended for calculating factorials of very large numbers to avoid stack overflow errors. - The function does not perform type or value checking on the input `n`. Passing non-integer va...</t>
+          <t>- This function is designed for non-negative integers. Providing a negative number will cause infinite recursion, leading to a "Maximum call stack size exceeded" error. - Due to its recursive nature, calculating the factorial of very large numbers can also lead to a stack overflow error. For such cases, an iterative approach is recommended. - The function does not validate if the input is an integer. While it may produce a result for floating-point numbers, the factorial is mathematically def...</t>
         </is>
       </c>
     </row>
@@ -591,27 +591,27 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>greet(name)</t>
+          <t>greet</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>The `greet` function logs a personalized greeting message to the console.</t>
+          <t>The `greet` function logs a personalized greeting message to the web console.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>- `name` (String): The name to include in the greeting message.</t>
+          <t>- `name` (string): The name of the person to greet. This value will be embedded in the output message.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function provides a simple way to display a standardized greeting to the console. It takes a single parameter, `name`, which is expected to be a string. The core logic uses the `console.log` method to print a formatted string. The string is created using a template literal (enclosed in backticks `` ` ``), which allows for the direct embedding of variables. The value of the `name` parameter is interpolated into the string `Hello, ${name}!` to generate the final output message.</t>
+          <t>This function provides a simple way to display a standard greeting. It accepts a single argument, `name`. The core logic uses the `console.log` method to print a message to the browser's developer console or a Node.js terminal. The message is constructed using a JavaScript template literal (a string enclosed in backticks `` ` ``). This allows for easy embedding of variables directly into the string using the `${name}` syntax. When the function is called, the value passed as the `name` paramet...</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- This function does not return a value (`undefined`). Its primary purpose is to produce a side effect by printing output to the console. - While the function is designed to work with a string `name`, JavaScript's type coercion will convert non-string arguments into their string representation. For example, calling `greet(123)` will output "Hello, 123!".</t>
+          <t>- This function does not return any value; its sole purpose is to produce a side effect by logging output to the console. - While the `name` parameter is intended to be a string, JavaScript will attempt to convert any passed data type to its string representation. For example, passing the number `123` will result in the output "Hello, 123!".</t>
         </is>
       </c>
     </row>

--- a/script.xlsx
+++ b/script.xlsx
@@ -536,12 +536,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>This function takes two arguments, `a` and `b`, and returns their sum. It uses the standard addition operator (`+`) to perform the calculation. The function is a straightforward implementation of arithmetic addition for numeric inputs.</t>
+          <t>This function takes two parameters, `a` and `b`, and returns their sum. It uses the standard addition operator (`+`) to perform the calculation. The function directly returns the result of the `a + b` operation.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>- This function is designed to work with numeric types (integers or floating-point numbers). - If strings are passed as arguments, the `+` operator will perform string concatenation instead of numeric addition due to JavaScript's type coercion. For example, `add("2", "3")` would result in `"23"`. - To ensure proper addition, make sure both inputs are numbers before calling the function. **Output Example**: The function returns a single `number` which is the sum of the two input parameters.</t>
+          <t>- While designed for numbers, the `+` operator in JavaScript will perform string concatenation if one or both of the operands are strings. For example, `add(5, "5")` would result in `"55"`. - The function does not include any type checking or error handling. It is the caller's responsibility to ensure that both arguments are of the `Number` type for a predictable arithmetic result. **Output Example**: The function returns a single `Number` which is the sum of the two input parameters.</t>
         </is>
       </c>
     </row>
@@ -561,22 +561,22 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>The `factorial` function recursively calculates the factorial of a given non-negative integer.</t>
+          <t>The `factorial` function recursively calculates the factorial of a given non-negative integer `n`.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>- `n` (Number): The non-negative integer whose factorial is to be calculated.</t>
+          <t>- `n` (Number): The non-negative integer for which the factorial will be calculated.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>This function implements the factorial operation using recursion. The logic is divided into two main parts: a base case and a recursive step. The function first evaluates the base case using a ternary operator: `n &lt;= 1 ? 1 : ...`. If the input number `n` is less than or equal to 1, the function immediately returns `1`. This is the termination condition for the recursion, as the factorial of 1 (1!) and 0 (0!) are both defined as 1. If `n` is greater than 1, the function executes the recursive ...</t>
+          <t>This function implements the factorial calculation using a recursive approach. The logic is based on the mathematical definition of a factorial, where the factorial of a non-negative integer `n` is the product of all positive integers up to `n`. The function operates as follows: - **Base Case:** It first checks if the input `n` is less than or equal to 1. If true, the function returns `1`. This serves as the termination condition for the recursion, as the factorial of 1 (`1!`) and 0 (`0!`) ar...</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>- This function is designed for non-negative integers. Providing a negative number will cause infinite recursion, leading to a "Maximum call stack size exceeded" error. - Due to its recursive nature, calculating the factorial of very large numbers can also lead to a stack overflow error. For such cases, an iterative approach is recommended. - The function does not validate if the input is an integer. While it may produce a result for floating-point numbers, the factorial is mathematically def...</t>
+          <t>- The function is intended for non-negative integers. Providing a negative number will cause an infinite recursion, leading to a stack overflow error. - The base case `n &lt;= 1` ensures that `factorial(0)` correctly returns `1`. - Be cautious with large input values. Deep recursion can lead to a "Maximum call stack size exceeded" error. Furthermore, the result can quickly grow larger than JavaScript's `Number.MAX_SAFE_INTEGER`, which may cause a loss of precision. **Output Example**: A single n...</t>
         </is>
       </c>
     </row>
@@ -596,22 +596,22 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>The `greet` function logs a personalized greeting message to the web console.</t>
+          <t>The `greet` function prints a personalized greeting message to the console.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>- `name` (string): The name of the person to greet. This value will be embedded in the output message.</t>
+          <t>- `name` (String): The name to be included in the greeting message.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This function provides a simple way to display a standard greeting. It accepts a single argument, `name`. The core logic uses the `console.log` method to print a message to the browser's developer console or a Node.js terminal. The message is constructed using a JavaScript template literal (a string enclosed in backticks `` ` ``). This allows for easy embedding of variables directly into the string using the `${name}` syntax. When the function is called, the value passed as the `name` paramet...</t>
+          <t>This function provides a simple way to display a standardized greeting to the console. It accepts a single string argument, `name`. The core logic uses the `console.log()` method to output a formatted string. The string is created using a template literal: `` `Hello, ${name}!` ``. This syntax allows for string interpolation, where the value of the `name` parameter is directly embedded into the output string, creating a personalized message. The function does not return any value; its only pur...</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>- This function does not return any value; its sole purpose is to produce a side effect by logging output to the console. - While the `name` parameter is intended to be a string, JavaScript will attempt to convert any passed data type to its string representation. For example, passing the number `123` will result in the output "Hello, 123!".</t>
+          <t>- The output of this function is directed to the standard console, such as a browser's developer console or a Node.js terminal. It does not render content on a webpage. - While a string is the expected type for the `name` parameter, JavaScript's type coercion will attempt to convert other data types (like numbers or objects) into a string representation when they are passed.</t>
         </is>
       </c>
     </row>

--- a/script.xlsx
+++ b/script.xlsx
@@ -467,10 +467,10 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -524,26 +524,10 @@
           <t>add</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>The `add` function computes the sum of two numbers.</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Description | The first number to be added. | The second number to be added. |</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>This function takes two parameters, `a` and `b`, and returns their sum. It uses the standard addition operator (`+`) to perform the calculation. The function directly returns the result of the `a + b` operation.</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>- While designed for numbers, the `+` operator in JavaScript will perform string concatenation if one or both of the operands are strings. For example, `add(5, "5")` would result in `"55"`. - The function does not include any type checking or error handling. It is the caller's responsibility to ensure that both arguments are of the `Number` type for a predictable arithmetic result. **Output Example**: The function returns a single `Number` which is the sum of the two input parameters.</t>
-        </is>
-      </c>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="4" t="n">
@@ -559,26 +543,10 @@
           <t>factorial</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>The `factorial` function recursively calculates the factorial of a given non-negative integer `n`.</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>- `n` (Number): The non-negative integer for which the factorial will be calculated.</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>This function implements the factorial calculation using a recursive approach. The logic is based on the mathematical definition of a factorial, where the factorial of a non-negative integer `n` is the product of all positive integers up to `n`. The function operates as follows: - **Base Case:** It first checks if the input `n` is less than or equal to 1. If true, the function returns `1`. This serves as the termination condition for the recursion, as the factorial of 1 (`1!`) and 0 (`0!`) ar...</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>- The function is intended for non-negative integers. Providing a negative number will cause an infinite recursion, leading to a stack overflow error. - The base case `n &lt;= 1` ensures that `factorial(0)` correctly returns `1`. - Be cautious with large input values. Deep recursion can lead to a "Maximum call stack size exceeded" error. Furthermore, the result can quickly grow larger than JavaScript's `Number.MAX_SAFE_INTEGER`, which may cause a loss of precision. **Output Example**: A single n...</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="inlineStr"/>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -594,26 +562,10 @@
           <t>greet</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>The `greet` function prints a personalized greeting message to the console.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>- `name` (String): The name to be included in the greeting message.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>This function provides a simple way to display a standardized greeting to the console. It accepts a single string argument, `name`. The core logic uses the `console.log()` method to output a formatted string. The string is created using a template literal: `` `Hello, ${name}!` ``. This syntax allows for string interpolation, where the value of the `name` parameter is directly embedded into the output string, creating a personalized message. The function does not return any value; its only pur...</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>- The output of this function is directed to the standard console, such as a browser's developer console or a Node.js terminal. It does not render content on a webpage. - While a string is the expected type for the `name` parameter, JavaScript's type coercion will attempt to convert other data types (like numbers or objects) into a string representation when they are passed.</t>
-        </is>
-      </c>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
